--- a/Llamen a Dios/Resources/Plantilla Proyeccion y Metas.xlsx
+++ b/Llamen a Dios/Resources/Plantilla Proyeccion y Metas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sonku\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CCDD595A-0D64-4620-8D45-681F44084FB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{509E3DBA-D30E-4A6B-BE9E-68AAB8A992E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{851E33CF-4BD8-4892-92A7-4275EBAE4D21}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{851E33CF-4BD8-4892-92A7-4275EBAE4D21}"/>
   </bookViews>
   <sheets>
     <sheet name="Proyección Mensual" sheetId="1" r:id="rId1"/>
@@ -57,9 +57,6 @@
     <t>META ESTIMADA DE VENTAS DIARIAS EN CAJA</t>
   </si>
   <si>
-    <t>Fecha (AGOSTO 2026)</t>
-  </si>
-  <si>
     <t>Meta de Ingresos a Facturar</t>
   </si>
   <si>
@@ -75,10 +72,13 @@
     <t>Por:</t>
   </si>
   <si>
-    <t>Direccion:</t>
-  </si>
-  <si>
     <t>Crecimiento Estimado</t>
+  </si>
+  <si>
+    <t>Direccion:   Av Jóvito Villalba, 6316, Nueva Esparta</t>
+  </si>
+  <si>
+    <t>Fecha (MES - AÑO)</t>
   </si>
 </sst>
 </file>
@@ -161,31 +161,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -200,6 +181,24 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -228,7 +227,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>422360</xdr:colOff>
+      <xdr:colOff>833840</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>175770</xdr:rowOff>
     </xdr:to>
@@ -647,47 +646,49 @@
   <dimension ref="A2:D18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29" customWidth="1"/>
+    <col min="1" max="1" width="16.77734375" customWidth="1"/>
+    <col min="2" max="2" width="23.109375" customWidth="1"/>
+    <col min="3" max="3" width="20.44140625" customWidth="1"/>
+    <col min="4" max="4" width="28.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="10"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C3" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="5"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C3" s="6" t="s">
+      <c r="D3" s="11"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C4" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="6"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C4" s="9" t="s">
+      <c r="D4" s="12"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C5" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="9"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C5" t="s">
-        <v>10</v>
-      </c>
+      <c r="D5" s="14"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C6" t="s">
+      <c r="C6" s="14" t="s">
         <v>11</v>
       </c>
+      <c r="D6" s="14"/>
     </row>
     <row r="9" spans="1:4" ht="18" x14ac:dyDescent="0.35">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
@@ -697,7 +698,7 @@
         <v>2</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>3</v>
@@ -732,14 +733,17 @@
       <c r="D18" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="6">
     <mergeCell ref="A9:D9"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C5:D5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -750,189 +754,197 @@
   <cols>
     <col min="1" max="1" width="25.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="31.44140625" customWidth="1"/>
-    <col min="3" max="3" width="17.33203125" customWidth="1"/>
+    <col min="3" max="3" width="18.6640625" customWidth="1"/>
     <col min="4" max="4" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="15"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B3" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="7"/>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B3" s="8" t="s">
+      <c r="C3" s="11"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B4" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="8"/>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B4" s="10" t="s">
+      <c r="C4" s="12"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B5" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="10"/>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
+      <c r="C5" s="16"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B6" t="s">
+      <c r="B6" s="12" t="s">
         <v>11</v>
       </c>
+      <c r="C6" s="12"/>
     </row>
     <row r="10" spans="1:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="11"/>
+      <c r="B10" s="13"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="12" t="s">
+      <c r="A12" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="12" t="s">
-        <v>6</v>
-      </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="7"/>
-      <c r="B13" s="13"/>
+      <c r="A13" s="4"/>
+      <c r="B13" s="6"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="7"/>
-      <c r="B14" s="13"/>
+      <c r="A14" s="4"/>
+      <c r="B14" s="6"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="7"/>
-      <c r="B15" s="13"/>
+      <c r="A15" s="4"/>
+      <c r="B15" s="6"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="7"/>
-      <c r="B16" s="13"/>
+      <c r="A16" s="4"/>
+      <c r="B16" s="6"/>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="7"/>
-      <c r="B17" s="13"/>
+      <c r="A17" s="4"/>
+      <c r="B17" s="6"/>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="7"/>
-      <c r="B18" s="13"/>
+      <c r="A18" s="4"/>
+      <c r="B18" s="6"/>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="7"/>
-      <c r="B19" s="13"/>
+      <c r="A19" s="4"/>
+      <c r="B19" s="6"/>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="7"/>
-      <c r="B20" s="13"/>
+      <c r="A20" s="4"/>
+      <c r="B20" s="6"/>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" s="7"/>
-      <c r="B21" s="13"/>
+      <c r="A21" s="4"/>
+      <c r="B21" s="6"/>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" s="7"/>
-      <c r="B22" s="13"/>
+      <c r="A22" s="4"/>
+      <c r="B22" s="6"/>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" s="7"/>
-      <c r="B23" s="13"/>
+      <c r="A23" s="4"/>
+      <c r="B23" s="6"/>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" s="7"/>
-      <c r="B24" s="13"/>
+      <c r="A24" s="4"/>
+      <c r="B24" s="6"/>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" s="7"/>
-      <c r="B25" s="13"/>
+      <c r="A25" s="4"/>
+      <c r="B25" s="6"/>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" s="7"/>
-      <c r="B26" s="13"/>
+      <c r="A26" s="4"/>
+      <c r="B26" s="6"/>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" s="7"/>
-      <c r="B27" s="13"/>
+      <c r="A27" s="4"/>
+      <c r="B27" s="6"/>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28" s="7"/>
-      <c r="B28" s="13"/>
+      <c r="A28" s="4"/>
+      <c r="B28" s="6"/>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" s="7"/>
-      <c r="B29" s="13"/>
+      <c r="A29" s="4"/>
+      <c r="B29" s="6"/>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30" s="7"/>
-      <c r="B30" s="13"/>
+      <c r="A30" s="4"/>
+      <c r="B30" s="6"/>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A31" s="7"/>
-      <c r="B31" s="13"/>
+      <c r="A31" s="4"/>
+      <c r="B31" s="6"/>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A32" s="7"/>
-      <c r="B32" s="13"/>
+      <c r="A32" s="4"/>
+      <c r="B32" s="6"/>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33" s="7"/>
-      <c r="B33" s="13"/>
+      <c r="A33" s="4"/>
+      <c r="B33" s="6"/>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34" s="7"/>
-      <c r="B34" s="13"/>
+      <c r="A34" s="4"/>
+      <c r="B34" s="6"/>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35" s="7"/>
-      <c r="B35" s="13"/>
+      <c r="A35" s="4"/>
+      <c r="B35" s="6"/>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" s="7"/>
-      <c r="B36" s="13"/>
+      <c r="A36" s="4"/>
+      <c r="B36" s="6"/>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" s="7"/>
-      <c r="B37" s="13"/>
+      <c r="A37" s="4"/>
+      <c r="B37" s="6"/>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" s="7"/>
-      <c r="B38" s="13"/>
+      <c r="A38" s="4"/>
+      <c r="B38" s="6"/>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" s="7"/>
-      <c r="B39" s="13"/>
+      <c r="A39" s="4"/>
+      <c r="B39" s="6"/>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" s="7"/>
-      <c r="B40" s="13"/>
+      <c r="A40" s="4"/>
+      <c r="B40" s="6"/>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A41" s="7"/>
-      <c r="B41" s="13"/>
+      <c r="A41" s="4"/>
+      <c r="B41" s="6"/>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A42" s="7"/>
-      <c r="B42" s="13"/>
+      <c r="A42" s="4"/>
+      <c r="B42" s="6"/>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A43" s="7"/>
-      <c r="B43" s="13"/>
+      <c r="A43" s="4"/>
+      <c r="B43" s="6"/>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A44" s="14"/>
-      <c r="B44" s="15"/>
+      <c r="A44" s="7"/>
+      <c r="B44" s="8"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="6">
     <mergeCell ref="A10:B10"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>